--- a/Códigos.xlsx
+++ b/Códigos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leonardo.pires\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leonardo.pires\Projetos Clube\conciliador_contabil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A960DB8C-CA3B-4E33-8323-8B5DD4F6E596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D3C78A-6E83-4E76-9138-1FEE3CA9C4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{FE19485B-6808-4D0E-B871-B3653A51B60A}"/>
+    <workbookView xWindow="23880" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{FE19485B-6808-4D0E-B871-B3653A51B60A}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="365">
   <si>
     <t>Conta</t>
   </si>
@@ -1117,6 +1117,24 @@
   </si>
   <si>
     <t>Contabil</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>0601</t>
+  </si>
+  <si>
+    <t>Sauna Feminina</t>
+  </si>
+  <si>
+    <t>3512</t>
+  </si>
+  <si>
+    <t>Eventos Tenis</t>
+  </si>
+  <si>
+    <t>Natação - Treinamentos E Clínicas</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1256,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1282,6 +1300,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4158,7 +4177,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D1AA03-D689-431C-86C6-5F5DE7F1DABA}">
-  <dimension ref="A1:C213"/>
+  <dimension ref="A1:C216"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="41.28515625" bestFit="1" customWidth="1"/>
@@ -5280,121 +5299,121 @@
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>141</v>
+      <c r="A104" s="19" t="s">
+        <v>360</v>
       </c>
       <c r="B104" t="s">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="C104">
-        <v>15190</v>
+        <v>15507</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B105" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C105">
-        <v>15185</v>
+        <v>15190</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>283</v>
+        <v>142</v>
       </c>
       <c r="B106" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="C106">
-        <v>15171</v>
+        <v>15185</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="B107" t="s">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="C107">
-        <v>15208</v>
+        <v>15171</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="B108" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="C108">
-        <v>15213</v>
+        <v>15208</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>143</v>
+        <v>265</v>
       </c>
       <c r="B109" t="s">
-        <v>163</v>
+        <v>266</v>
       </c>
       <c r="C109">
-        <v>15241</v>
+        <v>15213</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="B110" t="s">
-        <v>258</v>
+        <v>163</v>
       </c>
       <c r="C110">
-        <v>15185</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>144</v>
+        <v>257</v>
       </c>
       <c r="B111" t="s">
-        <v>172</v>
+        <v>258</v>
       </c>
       <c r="C111">
-        <v>15241</v>
+        <v>15185</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>285</v>
+        <v>144</v>
       </c>
       <c r="B112" t="s">
-        <v>286</v>
+        <v>172</v>
       </c>
       <c r="C112">
-        <v>15213</v>
+        <v>15241</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B113" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C113">
-        <v>15171</v>
+        <v>15213</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B114" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="C114">
         <v>15171</v>
@@ -5402,10 +5421,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>145</v>
+        <v>259</v>
       </c>
       <c r="B115" t="s">
-        <v>164</v>
+        <v>260</v>
       </c>
       <c r="C115">
         <v>15171</v>
@@ -5413,10 +5432,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>275</v>
+        <v>145</v>
       </c>
       <c r="B116" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="C116">
         <v>15171</v>
@@ -5424,403 +5443,403 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B117" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C117">
-        <v>15213</v>
+        <v>15171</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>40</v>
+        <v>281</v>
       </c>
       <c r="B118" t="s">
-        <v>41</v>
+        <v>282</v>
       </c>
       <c r="C118">
-        <v>15918</v>
+        <v>15213</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="B119" t="s">
-        <v>165</v>
+        <v>41</v>
       </c>
       <c r="C119">
-        <v>34548</v>
+        <v>15918</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>312</v>
+        <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
       <c r="C120">
-        <v>34922</v>
+        <v>34548</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="B121" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="C121">
-        <v>38505</v>
+        <v>34922</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>42</v>
+        <v>291</v>
       </c>
       <c r="B122" t="s">
-        <v>43</v>
+        <v>292</v>
       </c>
       <c r="C122">
-        <v>37170</v>
+        <v>38505</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>139</v>
+        <v>42</v>
       </c>
       <c r="B123" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="C123">
-        <v>4321</v>
+        <v>37170</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="B124" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="C124">
-        <v>39133</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B125" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C125">
-        <v>39154</v>
+        <v>39133</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="B126" t="s">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="C126">
-        <v>16294</v>
+        <v>39154</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>308</v>
+        <v>183</v>
       </c>
       <c r="B127" t="s">
-        <v>309</v>
+        <v>184</v>
       </c>
       <c r="C127">
-        <v>37331</v>
+        <v>16294</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>119</v>
+        <v>308</v>
       </c>
       <c r="B128" t="s">
-        <v>120</v>
+        <v>309</v>
       </c>
       <c r="C128">
-        <v>39469</v>
+        <v>37331</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="C129">
-        <v>39502</v>
+        <v>39469</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B130" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C130">
-        <v>39843</v>
+        <v>39502</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B131" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C131">
-        <v>39838</v>
+        <v>39843</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>198</v>
+        <v>52</v>
       </c>
       <c r="B132" t="s">
-        <v>199</v>
+        <v>53</v>
       </c>
       <c r="C132">
-        <v>16796</v>
+        <v>39838</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="B133" t="s">
-        <v>55</v>
+        <v>199</v>
       </c>
       <c r="C133">
-        <v>40552</v>
+        <v>16796</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>244</v>
+        <v>54</v>
       </c>
       <c r="B134" t="s">
-        <v>245</v>
+        <v>55</v>
       </c>
       <c r="C134">
-        <v>34137</v>
+        <v>40552</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>56</v>
+        <v>244</v>
       </c>
       <c r="B135" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C135">
-        <v>40755</v>
+        <v>34137</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B136" t="s">
-        <v>58</v>
+        <v>249</v>
       </c>
       <c r="C136">
-        <v>40888</v>
+        <v>40755</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>310</v>
+        <v>57</v>
       </c>
       <c r="B137" t="s">
-        <v>311</v>
+        <v>58</v>
       </c>
       <c r="C137">
-        <v>41362</v>
+        <v>40888</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>310</v>
+      </c>
+      <c r="B138" t="s">
+        <v>311</v>
+      </c>
+      <c r="C138">
+        <v>41362</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>190</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B139" t="s">
         <v>191</v>
       </c>
-      <c r="C138">
+      <c r="C139">
         <v>40713</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
         <v>1098</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B140" t="s">
         <v>169</v>
       </c>
-      <c r="C139">
+      <c r="C140">
         <v>40781</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>146</v>
-      </c>
-      <c r="B140" t="s">
-        <v>147</v>
-      </c>
-      <c r="C140">
-        <v>40872</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="C141">
-        <v>40867</v>
+        <v>40872</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B142" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C142">
-        <v>40921</v>
+        <v>40867</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B143" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C143">
-        <v>40638</v>
+        <v>40921</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>273</v>
+      <c r="A144" s="19" t="s">
+        <v>359</v>
       </c>
       <c r="B144" t="s">
-        <v>274</v>
+        <v>364</v>
       </c>
       <c r="C144">
-        <v>41341</v>
+        <v>41203</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>267</v>
+        <v>63</v>
       </c>
       <c r="B145" t="s">
-        <v>268</v>
+        <v>64</v>
       </c>
       <c r="C145">
-        <v>41731</v>
+        <v>40638</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="B146" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="C146">
-        <v>15869</v>
+        <v>41341</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="B147" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="C147">
-        <v>15799</v>
+        <v>41731</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>241</v>
+        <v>299</v>
       </c>
       <c r="B148" t="s">
-        <v>242</v>
+        <v>300</v>
       </c>
       <c r="C148">
-        <v>28778</v>
+        <v>15869</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="B149" t="s">
-        <v>66</v>
+        <v>251</v>
       </c>
       <c r="C149">
-        <v>15671</v>
+        <v>15799</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>121</v>
+        <v>241</v>
       </c>
       <c r="B150" t="s">
-        <v>122</v>
+        <v>242</v>
       </c>
       <c r="C150">
-        <v>15806</v>
+        <v>28778</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151">
-        <v>1501</v>
+      <c r="A151" t="s">
+        <v>65</v>
       </c>
       <c r="B151" t="s">
-        <v>252</v>
+        <v>66</v>
       </c>
       <c r="C151">
-        <v>16728</v>
+        <v>15671</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="B152" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="C152">
-        <v>15645</v>
+        <v>15806</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>301</v>
+      <c r="A153">
+        <v>1501</v>
       </c>
       <c r="B153" t="s">
         <v>252</v>
@@ -5831,32 +5850,32 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>338</v>
+        <v>67</v>
       </c>
       <c r="B154" t="s">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="C154">
-        <v>4321</v>
+        <v>15645</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="B155" t="s">
-        <v>345</v>
+        <v>252</v>
       </c>
       <c r="C155">
-        <v>4321</v>
+        <v>16728</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B156" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C156">
         <v>4321</v>
@@ -5864,10 +5883,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="B157" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="C157">
         <v>4321</v>
@@ -5875,21 +5894,21 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>269</v>
+        <v>339</v>
       </c>
       <c r="B158" t="s">
-        <v>270</v>
+        <v>341</v>
       </c>
       <c r="C158">
-        <v>747</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="B159" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="C159">
         <v>4321</v>
@@ -5897,595 +5916,628 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="B160" t="s">
-        <v>303</v>
+        <v>270</v>
       </c>
       <c r="C160">
-        <v>4321</v>
+        <v>747</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="B161" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="C161">
-        <v>677</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>192</v>
+        <v>302</v>
       </c>
       <c r="B162" t="s">
-        <v>193</v>
+        <v>303</v>
       </c>
       <c r="C162">
-        <v>219</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>123</v>
+        <v>327</v>
       </c>
       <c r="B163" t="s">
-        <v>124</v>
+        <v>328</v>
       </c>
       <c r="C163">
-        <v>203</v>
+        <v>677</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164">
-        <v>1706</v>
+      <c r="A164" t="s">
+        <v>192</v>
       </c>
       <c r="B164" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="C164">
-        <v>682</v>
+        <v>219</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="B165" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="C165">
-        <v>15853</v>
+        <v>203</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>71</v>
+      <c r="A166">
+        <v>1706</v>
       </c>
       <c r="B166" t="s">
-        <v>72</v>
+        <v>322</v>
       </c>
       <c r="C166">
-        <v>27578</v>
+        <v>682</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B167" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C167">
-        <v>41301</v>
+        <v>15853</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B168" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C168">
-        <v>28650</v>
+        <v>27578</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C169">
-        <v>28650</v>
+        <v>41301</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>331</v>
+        <v>75</v>
       </c>
       <c r="B170" t="s">
-        <v>332</v>
+        <v>76</v>
       </c>
       <c r="C170">
-        <v>31385</v>
+        <v>28650</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>336</v>
+        <v>77</v>
       </c>
       <c r="B171" t="s">
-        <v>337</v>
+        <v>78</v>
       </c>
       <c r="C171">
-        <v>31390</v>
+        <v>28650</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="B172" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="C172">
-        <v>747</v>
+        <v>31385</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>253</v>
+        <v>336</v>
       </c>
       <c r="B173" t="s">
-        <v>254</v>
+        <v>337</v>
       </c>
       <c r="C173">
-        <v>747</v>
+        <v>31390</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="B174" t="s">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="C174">
-        <v>16070</v>
+        <v>747</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>81</v>
+        <v>253</v>
       </c>
       <c r="B175" t="s">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="C175">
-        <v>16091</v>
+        <v>747</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="B176" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="C176">
-        <v>16065</v>
+        <v>16070</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>293</v>
+        <v>81</v>
       </c>
       <c r="B177" t="s">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="C177">
-        <v>29845</v>
+        <v>16091</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="B178" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C178">
-        <v>16051</v>
+        <v>16065</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>179</v>
+        <v>293</v>
       </c>
       <c r="B179" t="s">
-        <v>180</v>
+        <v>294</v>
       </c>
       <c r="C179">
-        <v>22134</v>
+        <v>29845</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B180" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C180">
-        <v>22176</v>
+        <v>16051</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C181">
-        <v>26997</v>
+        <v>22134</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>218</v>
+        <v>85</v>
       </c>
       <c r="B182" t="s">
-        <v>219</v>
+        <v>86</v>
       </c>
       <c r="C182">
-        <v>27599</v>
+        <v>22176</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>255</v>
+        <v>134</v>
       </c>
       <c r="B183" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C183">
-        <v>16476</v>
+        <v>26997</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>87</v>
+        <v>218</v>
       </c>
       <c r="B184" t="s">
-        <v>88</v>
+        <v>219</v>
       </c>
       <c r="C184">
-        <v>30047</v>
+        <v>27599</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>89</v>
+        <v>255</v>
       </c>
       <c r="B185" t="s">
-        <v>90</v>
+        <v>171</v>
       </c>
       <c r="C185">
-        <v>30052</v>
+        <v>16476</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="B186" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C186">
-        <v>33582</v>
+        <v>30047</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>349</v>
+        <v>89</v>
       </c>
       <c r="B187" t="s">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="C187">
-        <v>33689</v>
+        <v>30052</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="B188" t="s">
-        <v>92</v>
+        <v>168</v>
       </c>
       <c r="C188">
-        <v>36040</v>
+        <v>33582</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>188</v>
+        <v>349</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>350</v>
       </c>
       <c r="C189">
-        <v>36750</v>
+        <v>33689</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B190" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C190">
-        <v>37394</v>
+        <v>36040</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>256</v>
+        <v>188</v>
       </c>
       <c r="B191" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C191">
-        <v>34831</v>
+        <v>36750</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>217</v>
+        <v>93</v>
       </c>
       <c r="B192" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="C192">
-        <v>16177</v>
+        <v>37394</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>329</v>
+        <v>256</v>
       </c>
       <c r="B193" t="s">
-        <v>330</v>
+        <v>167</v>
       </c>
       <c r="C193">
-        <v>16177</v>
+        <v>34831</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>133</v>
+        <v>217</v>
       </c>
       <c r="B194" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="C194">
-        <v>16156</v>
+        <v>16177</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="B195" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="C195">
-        <v>19179</v>
+        <v>16177</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>290</v>
+        <v>133</v>
       </c>
       <c r="B196" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C196">
-        <v>33967</v>
+        <v>16156</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="B197" t="s">
-        <v>96</v>
+        <v>289</v>
       </c>
       <c r="C197">
-        <v>34499</v>
+        <v>19179</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>97</v>
+      <c r="A198" s="19" t="s">
+        <v>362</v>
       </c>
       <c r="B198" t="s">
-        <v>98</v>
+        <v>363</v>
       </c>
       <c r="C198">
-        <v>40568</v>
+        <v>16065</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="B199" t="s">
-        <v>324</v>
+        <v>128</v>
       </c>
       <c r="C199">
-        <v>16301</v>
+        <v>33967</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="B200" t="s">
-        <v>187</v>
+        <v>96</v>
       </c>
       <c r="C200">
-        <v>41383</v>
+        <v>34499</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>295</v>
+        <v>97</v>
       </c>
       <c r="B201" t="s">
-        <v>296</v>
+        <v>98</v>
       </c>
       <c r="C201">
-        <v>41801</v>
+        <v>40568</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="B202" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="C202">
-        <v>30052</v>
+        <v>16301</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>261</v>
+        <v>186</v>
       </c>
       <c r="B203" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="C203">
-        <v>16070</v>
+        <v>41383</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="B204" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="C204">
-        <v>22176</v>
+        <v>41801</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>297</v>
+        <v>263</v>
       </c>
       <c r="B205" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="C205">
-        <v>41817</v>
+        <v>30052</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>318</v>
+        <v>261</v>
       </c>
       <c r="B206" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="C206">
-        <v>41941</v>
+        <v>16070</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>346</v>
+        <v>271</v>
       </c>
       <c r="B207" t="s">
-        <v>347</v>
+        <v>272</v>
       </c>
       <c r="C207">
-        <v>4321</v>
+        <v>22176</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>342</v>
+        <v>297</v>
       </c>
       <c r="B208" t="s">
-        <v>343</v>
+        <v>298</v>
       </c>
       <c r="C208">
-        <v>41981</v>
+        <v>41817</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="B209" t="s">
-        <v>353</v>
+        <v>319</v>
       </c>
       <c r="C209">
-        <v>42055</v>
+        <v>41941</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="B210" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="C210">
-        <v>31385</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="B211" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C211">
-        <v>16754</v>
+        <v>41981</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>213</v>
+        <v>352</v>
       </c>
       <c r="B212" t="s">
-        <v>214</v>
+        <v>353</v>
       </c>
       <c r="C212">
-        <v>15073</v>
+        <v>42055</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>316</v>
+      </c>
+      <c r="B213" t="s">
+        <v>317</v>
+      </c>
+      <c r="C213">
+        <v>31385</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>320</v>
+      </c>
+      <c r="B214" t="s">
+        <v>321</v>
+      </c>
+      <c r="C214">
+        <v>16754</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>213</v>
+      </c>
+      <c r="B215" t="s">
+        <v>214</v>
+      </c>
+      <c r="C215">
+        <v>15073</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
         <v>215</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B216" t="s">
         <v>214</v>
       </c>
-      <c r="C213">
+      <c r="C216">
         <v>15073</v>
       </c>
     </row>
